--- a/output/pdf_financials_xlsx/EDT.xlsx
+++ b/output/pdf_financials_xlsx/EDT.xlsx
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.081</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -2096,10 +2096,10 @@
         <v>-4.076</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.489</v>
+        <v>-2.476</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.824</v>
+        <v>-4.743</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-9.066000000000001</v>
@@ -2218,10 +2218,10 @@
         <v>-3.854</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.259</v>
+        <v>-2.246</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.546</v>
+        <v>-4.465</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-8.762</v>
@@ -2279,10 +2279,10 @@
         <v>-105.0422458435541</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-58.828125</v>
+        <v>-58.48958333333333</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-158.5076708507671</v>
+        <v>-155.6834030683403</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>2.944</v>
@@ -2464,37 +2464,37 @@
         <v>10.054</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.369</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>4.368</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.435</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.807</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>8.414</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.414</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.988</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>4.071</v>
       </c>
     </row>
     <row r="35">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4</v>
+        <v>4.297</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.944</v>
@@ -2586,37 +2586,37 @@
         <v>10.054</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.369</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>4.368</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.435</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.807</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>8.414</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>8.414</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.988</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>4.071</v>
       </c>
     </row>
     <row r="37">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.339</v>
+        <v>0.042</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.045</v>
@@ -3318,37 +3318,37 @@
         <v>0.185</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.51</v>
+        <v>0.141</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.246</v>
+        <v>0.166</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.246</v>
+        <v>0.166</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.686</v>
+        <v>0.318</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.109</v>
+        <v>0.674</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.196</v>
+        <v>0.389</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.765000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>8.69</v>
+        <v>0.276</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.69</v>
+        <v>0.276</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.778</v>
+        <v>0.79</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>4.711</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="49">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -27296,7 +27296,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -52088,7 +52088,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -55482,7 +55482,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -62094,7 +62094,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -68518,7 +68518,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">

--- a/output/pdf_financials_xlsx/EDT.xlsx
+++ b/output/pdf_financials_xlsx/EDT.xlsx
@@ -2166,13 +2166,13 @@
         <v>0.304</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.246</v>
+        <v>0.294</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.225</v>
+        <v>0.272</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.21</v>
+        <v>0.218</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.178</v>
@@ -2227,13 +2227,13 @@
         <v>-8.762</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-8.510999999999999</v>
+        <v>-8.462999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-11.031</v>
+        <v>-10.984</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-15.427</v>
+        <v>-15.419</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-15.224</v>
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-426.4028056112225</v>
+        <v>-423.9979959919839</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-661.7276544691061</v>
+        <v>-658.9082183563288</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-965.3942428035044</v>
+        <v>-964.8936170212766</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>-58553.84615384616</v>
@@ -6545,40 +6545,40 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -6586,13 +6586,13 @@
         </is>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101">
@@ -7313,28 +7313,28 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="P112" s="1" t="inlineStr">
         <is>
@@ -28558,7 +28558,11 @@
           <t>Depreciation on right-of-use asset 10</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -28660,7 +28664,11 @@
           <t>Depreciation on property and equipment 11</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28764,7 +28772,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -34046,7 +34054,11 @@
           <t>Depreciation on right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34150,7 +34162,11 @@
           <t>Depreciation on property and equipment 10</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34252,7 +34268,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -35088,7 +35104,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36008,7 +36028,11 @@
           <t>Depreciation on right-of-use asset 11</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36114,7 +36138,11 @@
           <t>Depreciation on property and equipment 12</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -36220,7 +36248,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -36750,7 +36778,11 @@
           <t>Loss on disposal of property and equipment 12</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -38434,7 +38466,11 @@
           <t>Proceeds on disposal of property and equipment 10</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -39064,7 +39100,11 @@
           <t>Depreciation on property and equipment 9</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39164,7 +39204,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -39562,7 +39602,11 @@
           <t>Proceeds on disposal of property and equipment 9</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -39982,7 +40026,11 @@
           <t>Loss on disposal of property and equipment 9</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -41866,7 +41914,11 @@
           <t>Depreciation on property, plant, and equipment</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -41968,7 +42020,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -42910,7 +42962,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -57914,7 +57966,11 @@
           <t>Depreciation on right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -58016,7 +58072,11 @@
           <t>Depreciation on property and equipment 10</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -58120,7 +58180,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
